--- a/src/test/resources/testdata.xlsx
+++ b/src/test/resources/testdata.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maiya\IdeaProjects\KDE\src\test\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maiya\IdeaProjects\keyword_driven_framework_TestNG\src\test\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{191099FB-1E18-48C6-AB1A-23D2C005334F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECAE57CD-6754-4838-849D-E3E44FBE246A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{8751E216-6B08-4D68-A5A1-62EEF9F6395D}"/>
   </bookViews>

--- a/src/test/resources/testdata.xlsx
+++ b/src/test/resources/testdata.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maiya\IdeaProjects\keyword_driven_framework_TestNG\src\test\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECAE57CD-6754-4838-849D-E3E44FBE246A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF15EEC4-E803-4B7D-826D-D522A6BC075A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{8751E216-6B08-4D68-A5A1-62EEF9F6395D}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="51">
   <si>
     <t>TestScenario</t>
   </si>
@@ -152,6 +152,42 @@
   </si>
   <si>
     <t>1200004</t>
+  </si>
+  <si>
+    <t>TD_3.1.1</t>
+  </si>
+  <si>
+    <t>TD_3.1.2</t>
+  </si>
+  <si>
+    <t>Test Scenario - Transaction Operations</t>
+  </si>
+  <si>
+    <t>Test case - Transfer Funds</t>
+  </si>
+  <si>
+    <t>From Account</t>
+  </si>
+  <si>
+    <t>To Account</t>
+  </si>
+  <si>
+    <t>Amount</t>
+  </si>
+  <si>
+    <t>TXNPOST</t>
+  </si>
+  <si>
+    <t>TD_3.1.3</t>
+  </si>
+  <si>
+    <t>5000</t>
+  </si>
+  <si>
+    <t>1500</t>
+  </si>
+  <si>
+    <t>250</t>
   </si>
 </sst>
 </file>
@@ -510,7 +546,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{719DA03D-F223-4224-9FBE-01F8C83865E4}">
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="15.88671875" customWidth="1"/>
@@ -736,7 +772,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>2</v>
       </c>
@@ -756,7 +792,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>2</v>
       </c>
@@ -776,7 +812,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>2</v>
       </c>
@@ -796,7 +832,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>2</v>
       </c>
@@ -814,6 +850,111 @@
       </c>
       <c r="F20">
         <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>0</v>
+      </c>
+      <c r="B21" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>1</v>
+      </c>
+      <c r="B22" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>8</v>
+      </c>
+      <c r="B23" t="s">
+        <v>19</v>
+      </c>
+      <c r="C23" t="s">
+        <v>9</v>
+      </c>
+      <c r="D23" t="s">
+        <v>33</v>
+      </c>
+      <c r="E23" t="s">
+        <v>43</v>
+      </c>
+      <c r="F23" t="s">
+        <v>44</v>
+      </c>
+      <c r="G23" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>2</v>
+      </c>
+      <c r="B24" t="s">
+        <v>39</v>
+      </c>
+      <c r="C24" t="s">
+        <v>46</v>
+      </c>
+      <c r="E24">
+        <v>1</v>
+      </c>
+      <c r="F24">
+        <v>2</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>2</v>
+      </c>
+      <c r="B25" t="s">
+        <v>40</v>
+      </c>
+      <c r="C25" t="s">
+        <v>46</v>
+      </c>
+      <c r="D25" t="s">
+        <v>39</v>
+      </c>
+      <c r="E25">
+        <v>2</v>
+      </c>
+      <c r="F25">
+        <v>3</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>2</v>
+      </c>
+      <c r="B26" t="s">
+        <v>47</v>
+      </c>
+      <c r="C26" t="s">
+        <v>46</v>
+      </c>
+      <c r="D26" t="s">
+        <v>40</v>
+      </c>
+      <c r="E26">
+        <v>3</v>
+      </c>
+      <c r="F26">
+        <v>4</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>50</v>
       </c>
     </row>
   </sheetData>

--- a/src/test/resources/testdata.xlsx
+++ b/src/test/resources/testdata.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maiya\IdeaProjects\keyword_driven_framework_TestNG\src\test\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF15EEC4-E803-4B7D-826D-D522A6BC075A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34D53CF5-DCE2-4451-8727-DFE208767737}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{8751E216-6B08-4D68-A5A1-62EEF9F6395D}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="59">
   <si>
     <t>TestScenario</t>
   </si>
@@ -188,6 +188,30 @@
   </si>
   <si>
     <t>250</t>
+  </si>
+  <si>
+    <t>001</t>
+  </si>
+  <si>
+    <t>002</t>
+  </si>
+  <si>
+    <t>003</t>
+  </si>
+  <si>
+    <t>004</t>
+  </si>
+  <si>
+    <t>005</t>
+  </si>
+  <si>
+    <t>TD_1.1.1,TD_1.1.2</t>
+  </si>
+  <si>
+    <t>TD_1.1.2,TD_1.1.3</t>
+  </si>
+  <si>
+    <t>TD_1.1.3,TD_1.1.4</t>
   </si>
 </sst>
 </file>
@@ -550,7 +574,8 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="15.88671875" customWidth="1"/>
-    <col min="3" max="4" width="15.33203125" customWidth="1"/>
+    <col min="3" max="3" width="15.33203125" customWidth="1"/>
+    <col min="4" max="4" width="16.6640625" customWidth="1"/>
     <col min="5" max="5" width="15.77734375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -768,8 +793,8 @@
       <c r="E16" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="F16">
-        <v>1</v>
+      <c r="F16" s="1" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
@@ -788,8 +813,8 @@
       <c r="E17" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="F17">
-        <v>2</v>
+      <c r="F17" s="1" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
@@ -808,8 +833,8 @@
       <c r="E18" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="F18">
-        <v>3</v>
+      <c r="F18" s="1" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
@@ -828,8 +853,8 @@
       <c r="E19" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="F19">
-        <v>4</v>
+      <c r="F19" s="1" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
@@ -848,8 +873,8 @@
       <c r="E20" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="F20">
-        <v>5</v>
+      <c r="F20" s="1" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
@@ -901,11 +926,14 @@
       <c r="C24" t="s">
         <v>46</v>
       </c>
-      <c r="E24">
-        <v>1</v>
-      </c>
-      <c r="F24">
-        <v>2</v>
+      <c r="D24" t="s">
+        <v>56</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>52</v>
       </c>
       <c r="G24" s="1" t="s">
         <v>48</v>
@@ -922,13 +950,13 @@
         <v>46</v>
       </c>
       <c r="D25" t="s">
-        <v>39</v>
-      </c>
-      <c r="E25">
-        <v>2</v>
-      </c>
-      <c r="F25">
-        <v>3</v>
+        <v>57</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>53</v>
       </c>
       <c r="G25" s="1" t="s">
         <v>49</v>
@@ -945,13 +973,13 @@
         <v>46</v>
       </c>
       <c r="D26" t="s">
-        <v>40</v>
-      </c>
-      <c r="E26">
-        <v>3</v>
-      </c>
-      <c r="F26">
-        <v>4</v>
+        <v>58</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>54</v>
       </c>
       <c r="G26" s="1" t="s">
         <v>50</v>
